--- a/app/data/Knowledge_Base.xlsx
+++ b/app/data/Knowledge_Base.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,264 +441,682 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Worcester Bosch 4000</t>
+          <t>Centrica Enterprise Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>displays_error</t>
+          <t>powers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EA_Error</t>
+          <t>Agentic Knowledge Hub</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Flame not detected after ignition attempt.</t>
+          <t>Unified AI-powered intelligence layer for Centrica business knowledge, datasets, dashboards, and operational insights.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EA_Error</t>
+          <t>Sales_Funnel_Dataset</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>requires_part</t>
+          <t>managed_by_sme</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ignition Electrode</t>
+          <t>Sarah Jenkins (Head of Commercial Analytics)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Inspect lead connection, clean electrode or replace if worn.</t>
+          <t>Owner of commercial sales funnel, lead attribution, and conversion metrics in Snowflake.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EA_Error</t>
+          <t>Sales_Funnel_Dataset</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>requires_part</t>
+          <t>lineage_source</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gas Supply Valve</t>
+          <t>SAP IS-U &amp; Salesforce CRM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Check gas inlet pressure and solenoid valve coil resistance.</t>
+          <t>Aggregates raw customer leads and survey appointments from Salesforce into Snowflake data lake.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EA_Error</t>
+          <t>Live_Metrics_Dataset</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>caused_by</t>
+          <t>managed_by_sme</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Low Gas Pressure</t>
+          <t>David Ross (Lead Telemetry Engineer)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gas supply pressure at meter is below 18 mbar.</t>
+          <t>Maintains IoT grid pressure and thermal telemetry sensors across UK regions.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Low Gas Pressure</t>
+          <t>Live_Metrics_Dataset</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>remedy_step</t>
+          <t>lineage_source</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Check Emergency Control Valve</t>
+          <t>Grid Mon Substation IoT Network</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ensure main ECV valve handle is aligned parallel to gas pipe.</t>
+          <t>Real-time telemetry ingested via Kafka into Snowflake Operational Data Store.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Worcester Bosch 4000</t>
+          <t>Boiler_Installation_Forecast_v2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>displays_error</t>
+          <t>managed_by_sme</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>224_Error</t>
+          <t>Marcus Vance (Principal Data Scientist)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Primary flue thermostat or safety limiter tripped (&gt;105°C).</t>
+          <t>Predictive installation model using pipeline conversion, seasonal demand, and engineer capacity.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>224_Error</t>
+          <t>Boiler_Installation_Forecast_v2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>caused_by</t>
+          <t>consumes_dataset</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Overheating</t>
+          <t>Sales_Funnel_Dataset</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>System water flow restricted or pump air locked.</t>
+          <t>Uses qualified lead volume, kept appointment ratios, and quote conversion rates.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Overheating</t>
+          <t>Centrica_Executive_Dashboard</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>requires_part</t>
+          <t>managed_by_sme</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Circulating Pump</t>
+          <t>Claire Williams (VP Operations)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Verify pump impeller spin and clear air bleed valve.</t>
+          <t>PowerBI dashboard providing real-time visibility into sales conversion, telemetry alerts, and service activity.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ideal Logic Combi</t>
+          <t>Centrica_Executive_Dashboard</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>displays_error</t>
+          <t>displays_metrics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>F2_Error</t>
+          <t>Sales Conversion &amp; Grid Telemetry</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Flame loss during operation.</t>
+          <t>Unified view combining Commercial Sales Funnel and Live Telemetry Metrics.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F2_Error</t>
+          <t>Worcester Bosch 4000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>requires_part</t>
+          <t>displays_error</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Condensate Pipe</t>
+          <t>EA_Error</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Check for external ice blockage or kinked discharge pipe.</t>
+          <t>Flame was not detected after an ignition attempt.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Baxi 800 Combi</t>
+          <t>EA_Error</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>displays_error</t>
+          <t>requires_part</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>E119_Error</t>
+          <t>Ignition Electrode</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>System operating pressure below minimum threshold (&lt;0.5 bar).</t>
+          <t>Inspect the lead, clean the electrode, or replace it if worn.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>EA_Error</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>requires_part</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Gas Supply Valve</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Check inlet pressure and the solenoid valve coil resistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EA_Error</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>caused_by</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Low Gas Pressure</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Gas pressure at the meter is below 18 mbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Low Gas Pressure</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>remedy_step</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Check Emergency Control Valve</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ensure the main valve handle is parallel to the pipe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Worcester Bosch 4000</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>displays_error</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>224_Error</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>The primary flue thermostat or safety limiter has tripped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>224_Error</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>caused_by</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Overheating</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Water flow may be restricted or the pump may be air locked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Overheating</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>requires_part</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Circulating Pump</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Verify impeller movement and bleed trapped air.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ideal Logic Combi</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>displays_error</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>F2_Error</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Flame loss during operation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>F2_Error</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>requires_part</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Condensate Pipe</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Check for external ice blockage or a kinked discharge pipe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Baxi 800 Combi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>displays_error</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>E119_Error</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>System pressure is below the minimum operating threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>E119_Error</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>remedy_step</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Re-pressurise Filling Loop</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Attach filling loop hose and repressurise system gauge to 1.5 bar.</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Repressurise the system gauge to 1.5 bar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Home Energy Services</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>provides</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Heating Installation</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Design and fit replacement boilers, heating controls, and compatible system upgrades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Home Energy Services</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>provides</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Heating Repair</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Diagnose and repair boiler, radiator, thermostat, and hot-water faults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Home Energy Services</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>provides</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Annual Maintenance</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Carry out planned appliance servicing and safety checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Home Energy Services</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>provides</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Plumbing And Drains</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Repair leaks, taps, toilets, pipework, and common drainage issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Home Energy Services</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>provides</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Electrical Support</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Provide domestic electrical checks, fault diagnosis, and selected repairs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Home Energy Services</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>provides</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Appliance Care</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Repair and maintain selected kitchen and laundry appliances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>converts_to</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Net Appointment</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>A qualified prospect that results in a kept consultation or survey appointment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Net Appointment</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>converts_to</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Net Sale</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>A kept appointment that results in a completed, non-cancelled sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Net Sale</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>measured_by</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sales Conversion</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Net sales divided by qualified leads, expressed as a percentage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>supports</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Net Sale</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>A priced proposal issued for an installation, repair, or service plan.</t>
         </is>
       </c>
     </row>

--- a/app/data/Knowledge_Base.xlsx
+++ b/app/data/Knowledge_Base.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Centrica Enterprise Platform</t>
+          <t>ABC Enterprise Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unified AI-powered intelligence layer for Centrica business knowledge, datasets, dashboards, and operational insights.</t>
+          <t>Unified AI-powered intelligence layer for ABC business knowledge, datasets, dashboards, and operational insights.</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Centrica_Executive_Dashboard</t>
+          <t>ABC_Executive_Dashboard</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Centrica_Executive_Dashboard</t>
+          <t>ABC_Executive_Dashboard</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/app/data/Knowledge_Base.xlsx
+++ b/app/data/Knowledge_Base.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1035,86 +1035,152 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>EA_Error</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>converts_to</t>
+          <t>need_to_end_connection</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Net Appointment</t>
+          <t>Worcester Bosch 4000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A qualified prospect that results in a kept consultation or survey appointment.</t>
+          <t>Boiler must be isolated and power disconnected before any repair attempt — risk of electric shock and gas leak.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Net Appointment</t>
+          <t>224_Error</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>converts_to</t>
+          <t>need_to_end_connection</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Net Sale</t>
+          <t>Worcester Bosch 4000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A kept appointment that results in a completed, non-cancelled sale.</t>
+          <t>Overheating fault requires immediate shutdown and full system isolation before engineer intervention.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Net Sale</t>
+          <t>E119_Error</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>measured_by</t>
+          <t>need_to_end_connection</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sales Conversion</t>
+          <t>Baxi 800 Combi</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Net sales divided by qualified leads, expressed as a percentage.</t>
+          <t>Low pressure fault — isolate system and depressurise before opening any filling loop connections.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>converts_to</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Net Appointment</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>A qualified prospect that results in a kept consultation or survey appointment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Net Appointment</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>converts_to</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Net Sale</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A kept appointment that results in a completed, non-cancelled sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Net Sale</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>measured_by</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sales Conversion</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Net sales divided by qualified leads, expressed as a percentage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Quote</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>supports</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Net Sale</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>A priced proposal issued for an installation, repair, or service plan.</t>
         </is>

--- a/app/data/Knowledge_Base.xlsx
+++ b/app/data/Knowledge_Base.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1186,6 +1186,1678 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Agentic Knowledge Hub</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>powers</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>The central repository connecting all operational datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Customer Master</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Core customer demographic and account records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Customer Holdings</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Products, appliances, and services owned by the customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Property Master</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Address and structural details of serviced properties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Boiler Master</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Registry of boiler models, specifications, and lifecycles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Installation History</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Historical records of new appliance and system installations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Service History</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Logs of annual servicing and maintenance visits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Repair History</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Historical breakdowns, fault diagnoses, and resolution actions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Visit Outcomes</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Final statuses and notes from engineer property visits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Fault Codes</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Diagnostic error codes and corresponding resolutions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Parts Replaced</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Inventory of components consumed during repair visits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Engineer Master</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Profiles, regions, and certifications of field engineers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Engineer Skills</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Specific technical competencies and appliance accreditations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Engineer Availability &amp; Shifts</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Schedules, rotas, and current working status of engineers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Engineer Productivity</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Metrics on job completion rates, first-time fix, and efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Appointment Schedule</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Diary of booked customer visits and time slots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Contact Centre Interactions</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Logs of customer calls, chats, and support tickets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Product &amp; Warranty Information</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Terms, coverage periods, and conditions for appliances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Quotes &amp; Sales</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Commercial proposals, converted sales, and revenue data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Regional Demand Forecast</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Predictive models for upcoming service and installation volumes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Regional Capacity Plans</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Resource allocation and engineer coverage per territory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Knowledge Base (manuals, SOPs, troubleshooting guides)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Core repository of technical documentation and procedures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Inventory &amp; Van Stock</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Current levels of spare parts in warehouses and engineer vehicles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Weather Data</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Meteorological information impacting heating demand and travel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>EPC Property Data</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Energy Performance Certificate ratings and property efficiency details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge Base</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>integrated_dataset</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Business Rules (warranty, SLA, eligibility)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Logic governing service entitlements and operational compliance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Customer Master</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Customer Master Definition</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Contains core customer demographics, contact information, billing preferences, and primary account details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Customer Master</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SAP IS-U</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Central billing and customer information system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Customer Holdings</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Customer Holdings Definition</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Tracks the specific products, appliances, and service plans actively owned or subscribed to by the customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Customer Holdings</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SAP IS-U</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Central billing and customer information system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Property Master</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Property Master Definition</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Stores address details, structural characteristics, and access instructions for serviced properties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Property Master</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SAP IS-U</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Central billing and customer information system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Boiler Master</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Boiler Master Definition</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Registry of all supported boiler makes, models, technical specifications, and expected lifecycles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Boiler Master</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SAP ERP</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Enterprise Resource Planning system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Installation History</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Installation History Definition</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Historical log of new appliance and heating system installations, including dates and installer IDs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Installation History</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Salesforce CRM</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Customer Relationship Management system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Service History</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Service History Definition</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Log of all planned annual servicing and routine maintenance visits performed for a customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Service History</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Salesforce Service Cloud</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Service management and tracking system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Repair History</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Repair History Definition</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Record of all unplanned breakdowns, fault diagnoses, and the subsequent repair actions taken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Repair History</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Salesforce Service Cloud</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Service management and tracking system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Visit Outcomes</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Visit Outcomes Definition</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Final statuses, engineer notes, and customer signatures collected at the end of a property visit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Visit Outcomes</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Field Service Lightning</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Field service and dispatch management system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Fault Codes</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Fault Codes Definition</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Repository of diagnostic error codes generated by appliances and their corresponding resolution steps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Fault Codes</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SharePoint</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Enterprise document management and intranet portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Parts Replaced</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Parts Replaced Definition</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Inventory log of specific components and spare parts consumed during repair and maintenance visits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Parts Replaced</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SAP ERP</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Enterprise Resource Planning system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Engineer Master</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Engineer Master Definition</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>HR records containing engineer profiles, home regions, and basic employment details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Engineer Master</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Human Capital Management system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Engineer Skills</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Engineer Skills Definition</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Matrix of specific technical competencies, gas safety accreditations, and appliance repair certifications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Engineer Skills</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Human Capital Management system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Engineer Availability &amp; Shifts</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Engineer Availability Definition</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Real-time schedules, shift patterns, rotas, and current working status of field engineers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Engineer Availability &amp; Shifts</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Field Service Lightning</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Field service and dispatch management system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Engineer Productivity</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Engineer Productivity Definition</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Aggregated performance metrics including jobs completed per day, first-time fix rates, and efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Engineer Productivity</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Snowflake Analytics</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Enterprise data warehouse and analytics platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Appointment Schedule</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Appointment Schedule Definition</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>The master diary of booked customer visits, time slots, and assigned engineers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Appointment Schedule</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Field Service Lightning</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Field service and dispatch management system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Contact Centre Interactions</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Contact Centre Interactions Definition</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Transcripts and logs of customer phone calls, web chats, and support tickets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Contact Centre Interactions</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Cloud contact centre and telephony system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Product &amp; Warranty Information</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Product &amp; Warranty Information Definition</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Details of appliance terms, active coverage periods, and specific conditions for warranty claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Product &amp; Warranty Information</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Salesforce CRM</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Customer Relationship Management system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Quotes &amp; Sales</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Quotes &amp; Sales Definition</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Financial records of commercial proposals issued to customers and the resulting converted sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Quotes &amp; Sales</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Salesforce CRM</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Customer Relationship Management system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Regional Demand Forecast</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Regional Demand Forecast Definition</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Machine learning predictive models forecasting upcoming service and installation volume by territory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Regional Demand Forecast</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Snowflake Analytics</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Enterprise data warehouse and analytics platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Regional Capacity Plans</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Regional Capacity Plans Definition</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Strategic resource allocation models balancing available engineer coverage against forecasted demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Regional Capacity Plans</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Snowflake Analytics</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Enterprise data warehouse and analytics platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Knowledge Base (manuals, SOPs, troubleshooting guides)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Knowledge Base Definition</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>The core document management system hosting OEM technical manuals, SOPs, and troubleshooting guides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Knowledge Base (manuals, SOPs, troubleshooting guides)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SharePoint</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Enterprise document management and intranet portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Inventory &amp; Van Stock</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Inventory &amp; Van Stock Definition</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Live tracking of current spare part quantities across regional warehouses and individual engineer vehicles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Inventory &amp; Van Stock</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SAP ERP</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Enterprise Resource Planning system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Weather Data</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Weather Data Definition</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Third-party meteorological data used to correlate severe weather events with spikes in heating demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Weather Data</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Snowflake Data Lake</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Enterprise data warehouse and analytics platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>EPC Property Data</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EPC Property Data Definition</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Energy Performance Certificate ratings and property efficiency details imported from public registries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>EPC Property Data</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Snowflake Data Lake</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Enterprise data warehouse and analytics platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Business Rules (warranty, SLA, eligibility)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>has_definition</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Business Rules Definition</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Logic engine governing service entitlements, SLA compliance, and customer eligibility for repairs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Business Rules (warranty, SLA, eligibility)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>available_in</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Customer Relationship Management system.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
